--- a/public/data/2025-2026学年第二学期集中考试周1安排表（学校组织）-学生用表.xlsx
+++ b/public/data/2025-2026学年第二学期集中考试周1安排表（学校组织）-学生用表.xlsx
@@ -83,7 +83,7 @@
     <t>谭智一/傅杰</t>
   </si>
   <si>
-    <t>2026年04月29日(13:30-15:20)</t>
+    <t>2026年05月06日(13:30-15:20)</t>
   </si>
   <si>
     <t>锁金－604</t>
@@ -1313,12 +1313,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1669,7 +1675,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1693,16 +1699,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1711,89 +1717,89 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1807,6 +1813,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2413,7 +2422,7 @@
       <c r="G2" s="4">
         <v>1</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I2" s="4" t="s">
@@ -2451,7 +2460,7 @@
       <c r="G3" s="4">
         <v>2</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I3" s="4" t="s">
@@ -2489,7 +2498,7 @@
       <c r="G4" s="4">
         <v>1</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I4" s="4" t="s">
@@ -2527,7 +2536,7 @@
       <c r="G5" s="4">
         <v>1</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I5" s="4" t="s">
@@ -2565,7 +2574,7 @@
       <c r="G6" s="4">
         <v>1</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I6" s="4" t="s">
@@ -2603,7 +2612,7 @@
       <c r="G7" s="4">
         <v>37</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I7" s="4" t="s">
@@ -2641,7 +2650,7 @@
       <c r="G8" s="4">
         <v>36</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I8" s="4" t="s">
@@ -2679,7 +2688,7 @@
       <c r="G9" s="4">
         <v>31</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I9" s="4" t="s">
@@ -2717,7 +2726,7 @@
       <c r="G10" s="4">
         <v>36</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>18</v>
       </c>
       <c r="I10" s="4" t="s">
@@ -11919,13 +11928,13 @@
       <c r="I252" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="J252" s="5" t="s">
+      <c r="J252" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="K252" s="5">
+      <c r="K252" s="6">
         <v>2024</v>
       </c>
-      <c r="L252" s="5" t="s">
+      <c r="L252" s="6" t="s">
         <v>354</v>
       </c>
     </row>

--- a/public/data/2025-2026学年第二学期集中考试周1安排表（学校组织）-学生用表.xlsx
+++ b/public/data/2025-2026学年第二学期集中考试周1安排表（学校组织）-学生用表.xlsx
@@ -9,6 +9,9 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$L$255</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -27,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2522" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2552" uniqueCount="375">
   <si>
     <t>校区</t>
   </si>
@@ -1083,6 +1086,18 @@
   </si>
   <si>
     <t>B230212</t>
+  </si>
+  <si>
+    <t>B230222</t>
+  </si>
+  <si>
+    <t>柔性电子学</t>
+  </si>
+  <si>
+    <t>B230223</t>
+  </si>
+  <si>
+    <t>B230224</t>
   </si>
   <si>
     <t>B230301</t>
@@ -1546,9 +1561,7 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color indexed="0"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1799,7 +1812,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1818,7 +1831,13 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2346,7 +2365,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L252"/>
+  <dimension ref="A1:L255"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="7.25" style="2" customWidth="1"/>
@@ -10884,32 +10903,32 @@
       <c r="C225" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D225" s="4" t="s">
+      <c r="D225" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E225" s="4" t="s">
+      <c r="E225" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="F225" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="G225" s="4">
-        <v>32</v>
-      </c>
-      <c r="H225" s="4" t="s">
+      <c r="F225" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G225" s="6">
+        <v>21</v>
+      </c>
+      <c r="H225" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="I225" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="J225" s="4" t="s">
+      <c r="I225" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="J225" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K225" s="6">
+        <v>2023</v>
+      </c>
+      <c r="L225" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="K225" s="4">
-        <v>2023</v>
-      </c>
-      <c r="L225" s="4" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="226" spans="1:12">
@@ -10922,32 +10941,32 @@
       <c r="C226" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D226" s="4" t="s">
+      <c r="D226" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E226" s="4" t="s">
-        <v>355</v>
-      </c>
-      <c r="F226" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="G226" s="4">
-        <v>33</v>
-      </c>
-      <c r="H226" s="4" t="s">
+      <c r="E226" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="F226" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G226" s="6">
+        <v>26</v>
+      </c>
+      <c r="H226" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="I226" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="J226" s="4" t="s">
+      <c r="I226" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="J226" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K226" s="6">
+        <v>2023</v>
+      </c>
+      <c r="L226" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="K226" s="4">
-        <v>2023</v>
-      </c>
-      <c r="L226" s="4" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="227" spans="1:12">
@@ -10960,32 +10979,32 @@
       <c r="C227" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D227" s="4" t="s">
+      <c r="D227" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E227" s="4" t="s">
-        <v>356</v>
-      </c>
-      <c r="F227" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="G227" s="4">
-        <v>31</v>
-      </c>
-      <c r="H227" s="4" t="s">
+      <c r="E227" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="F227" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G227" s="6">
+        <v>22</v>
+      </c>
+      <c r="H227" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="I227" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="J227" s="4" t="s">
+      <c r="I227" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="J227" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="K227" s="6">
+        <v>2023</v>
+      </c>
+      <c r="L227" s="6" t="s">
         <v>353</v>
-      </c>
-      <c r="K227" s="4">
-        <v>2023</v>
-      </c>
-      <c r="L227" s="4" t="s">
-        <v>354</v>
       </c>
     </row>
     <row r="228" spans="1:12">
@@ -11002,7 +11021,7 @@
         <v>288</v>
       </c>
       <c r="E228" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F228" s="4" t="s">
         <v>303</v>
@@ -11014,16 +11033,16 @@
         <v>291</v>
       </c>
       <c r="I228" s="4" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="J228" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K228" s="4">
         <v>2023</v>
       </c>
       <c r="L228" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="229" spans="1:12">
@@ -11040,28 +11059,28 @@
         <v>288</v>
       </c>
       <c r="E229" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F229" s="4" t="s">
         <v>303</v>
       </c>
       <c r="G229" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H229" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I229" s="4" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="J229" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K229" s="4">
         <v>2023</v>
       </c>
       <c r="L229" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="230" spans="1:12">
@@ -11090,16 +11109,16 @@
         <v>291</v>
       </c>
       <c r="I230" s="4" t="s">
-        <v>361</v>
+        <v>304</v>
       </c>
       <c r="J230" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K230" s="4">
         <v>2023</v>
       </c>
       <c r="L230" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="231" spans="1:12">
@@ -11116,28 +11135,28 @@
         <v>288</v>
       </c>
       <c r="E231" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F231" s="4" t="s">
         <v>303</v>
       </c>
       <c r="G231" s="4">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H231" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I231" s="4" t="s">
-        <v>361</v>
+        <v>304</v>
       </c>
       <c r="J231" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K231" s="4">
         <v>2023</v>
       </c>
       <c r="L231" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="232" spans="1:12">
@@ -11154,28 +11173,28 @@
         <v>288</v>
       </c>
       <c r="E232" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F232" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G232" s="4">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H232" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I232" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="J232" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K232" s="4">
         <v>2023</v>
       </c>
       <c r="L232" s="4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="233" spans="1:12">
@@ -11195,25 +11214,25 @@
         <v>364</v>
       </c>
       <c r="F233" s="4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G233" s="4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H233" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I233" s="4" t="s">
-        <v>302</v>
+        <v>365</v>
       </c>
       <c r="J233" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K233" s="4">
         <v>2023</v>
       </c>
       <c r="L233" s="4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="234" spans="1:12">
@@ -11230,28 +11249,28 @@
         <v>288</v>
       </c>
       <c r="E234" s="4" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F234" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G234" s="4">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="H234" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I234" s="4" t="s">
-        <v>112</v>
+        <v>365</v>
       </c>
       <c r="J234" s="4" t="s">
-        <v>113</v>
+        <v>357</v>
       </c>
       <c r="K234" s="4">
         <v>2023</v>
       </c>
       <c r="L234" s="4" t="s">
-        <v>245</v>
+        <v>363</v>
       </c>
     </row>
     <row r="235" spans="1:12">
@@ -11268,28 +11287,28 @@
         <v>288</v>
       </c>
       <c r="E235" s="4" t="s">
-        <v>127</v>
+        <v>367</v>
       </c>
       <c r="F235" s="4" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="G235" s="4">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H235" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I235" s="4" t="s">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="J235" s="4" t="s">
-        <v>50</v>
+        <v>357</v>
       </c>
       <c r="K235" s="4">
         <v>2023</v>
       </c>
       <c r="L235" s="4" t="s">
-        <v>58</v>
+        <v>363</v>
       </c>
     </row>
     <row r="236" spans="1:12">
@@ -11306,28 +11325,28 @@
         <v>288</v>
       </c>
       <c r="E236" s="4" t="s">
-        <v>128</v>
+        <v>368</v>
       </c>
       <c r="F236" s="4" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="G236" s="4">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="H236" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I236" s="4" t="s">
-        <v>80</v>
+        <v>302</v>
       </c>
       <c r="J236" s="4" t="s">
-        <v>50</v>
+        <v>357</v>
       </c>
       <c r="K236" s="4">
         <v>2023</v>
       </c>
       <c r="L236" s="4" t="s">
-        <v>58</v>
+        <v>363</v>
       </c>
     </row>
     <row r="237" spans="1:12">
@@ -11344,28 +11363,28 @@
         <v>288</v>
       </c>
       <c r="E237" s="4" t="s">
-        <v>148</v>
+        <v>369</v>
       </c>
       <c r="F237" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G237" s="4">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="H237" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I237" s="4" t="s">
-        <v>361</v>
+        <v>112</v>
       </c>
       <c r="J237" s="4" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="K237" s="4">
         <v>2023</v>
       </c>
       <c r="L237" s="4" t="s">
-        <v>69</v>
+        <v>245</v>
       </c>
     </row>
     <row r="238" spans="1:12">
@@ -11382,28 +11401,28 @@
         <v>288</v>
       </c>
       <c r="E238" s="4" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="F238" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G238" s="4">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="H238" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I238" s="4" t="s">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="J238" s="4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="K238" s="4">
         <v>2023</v>
       </c>
       <c r="L238" s="4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="239" spans="1:12">
@@ -11420,28 +11439,28 @@
         <v>288</v>
       </c>
       <c r="E239" s="4" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="F239" s="4" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="G239" s="4">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H239" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I239" s="4" t="s">
-        <v>366</v>
+        <v>80</v>
       </c>
       <c r="J239" s="4" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="K239" s="4">
         <v>2023</v>
       </c>
       <c r="L239" s="4" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="240" spans="1:12">
@@ -11458,19 +11477,19 @@
         <v>288</v>
       </c>
       <c r="E240" s="4" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="F240" s="4" t="s">
         <v>303</v>
       </c>
       <c r="G240" s="4">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="H240" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I240" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="J240" s="4" t="s">
         <v>68</v>
@@ -11496,19 +11515,19 @@
         <v>288</v>
       </c>
       <c r="E241" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F241" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G241" s="4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H241" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I241" s="4" t="s">
-        <v>80</v>
+        <v>370</v>
       </c>
       <c r="J241" s="4" t="s">
         <v>68</v>
@@ -11534,10 +11553,10 @@
         <v>288</v>
       </c>
       <c r="E242" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F242" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G242" s="4">
         <v>32</v>
@@ -11546,7 +11565,7 @@
         <v>291</v>
       </c>
       <c r="I242" s="4" t="s">
-        <v>147</v>
+        <v>370</v>
       </c>
       <c r="J242" s="4" t="s">
         <v>68</v>
@@ -11555,7 +11574,7 @@
         <v>2023</v>
       </c>
       <c r="L242" s="4" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
     </row>
     <row r="243" spans="1:12">
@@ -11572,19 +11591,19 @@
         <v>288</v>
       </c>
       <c r="E243" s="4" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="F243" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="G243" s="4">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="H243" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I243" s="4" t="s">
-        <v>147</v>
+        <v>370</v>
       </c>
       <c r="J243" s="4" t="s">
         <v>68</v>
@@ -11593,7 +11612,7 @@
         <v>2023</v>
       </c>
       <c r="L243" s="4" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
     </row>
     <row r="244" spans="1:12">
@@ -11610,19 +11629,19 @@
         <v>288</v>
       </c>
       <c r="E244" s="4" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F244" s="4" t="s">
         <v>299</v>
       </c>
       <c r="G244" s="4">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H244" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I244" s="4" t="s">
-        <v>147</v>
+        <v>80</v>
       </c>
       <c r="J244" s="4" t="s">
         <v>68</v>
@@ -11631,12 +11650,12 @@
         <v>2023</v>
       </c>
       <c r="L244" s="4" t="s">
-        <v>155</v>
+        <v>69</v>
       </c>
     </row>
     <row r="245" spans="1:12">
       <c r="A245" s="4" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B245" s="4" t="s">
         <v>101</v>
@@ -11648,33 +11667,33 @@
         <v>288</v>
       </c>
       <c r="E245" s="4" t="s">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="F245" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G245" s="4">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H245" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I245" s="4" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="J245" s="4" t="s">
-        <v>182</v>
+        <v>68</v>
       </c>
       <c r="K245" s="4">
         <v>2023</v>
       </c>
       <c r="L245" s="4" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
     </row>
     <row r="246" spans="1:12">
       <c r="A246" s="4" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="B246" s="4" t="s">
         <v>101</v>
@@ -11686,28 +11705,28 @@
         <v>288</v>
       </c>
       <c r="E246" s="4" t="s">
-        <v>184</v>
+        <v>156</v>
       </c>
       <c r="F246" s="4" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="G246" s="4">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="H246" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I246" s="4" t="s">
-        <v>38</v>
+        <v>147</v>
       </c>
       <c r="J246" s="4" t="s">
-        <v>182</v>
+        <v>68</v>
       </c>
       <c r="K246" s="4">
         <v>2023</v>
       </c>
       <c r="L246" s="4" t="s">
-        <v>183</v>
+        <v>155</v>
       </c>
     </row>
     <row r="247" spans="1:12">
@@ -11724,33 +11743,33 @@
         <v>288</v>
       </c>
       <c r="E247" s="4" t="s">
-        <v>238</v>
+        <v>157</v>
       </c>
       <c r="F247" s="4" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="G247" s="4">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H247" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I247" s="4" t="s">
-        <v>367</v>
+        <v>147</v>
       </c>
       <c r="J247" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="K247" s="4">
         <v>2023</v>
       </c>
       <c r="L247" s="4" t="s">
-        <v>239</v>
+        <v>155</v>
       </c>
     </row>
     <row r="248" spans="1:12">
       <c r="A248" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B248" s="4" t="s">
         <v>101</v>
@@ -11762,33 +11781,33 @@
         <v>288</v>
       </c>
       <c r="E248" s="4" t="s">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="F248" s="4" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="G248" s="4">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H248" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I248" s="4" t="s">
-        <v>367</v>
+        <v>38</v>
       </c>
       <c r="J248" s="4" t="s">
-        <v>76</v>
+        <v>182</v>
       </c>
       <c r="K248" s="4">
         <v>2023</v>
       </c>
       <c r="L248" s="4" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
     </row>
     <row r="249" spans="1:12">
       <c r="A249" s="4" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="B249" s="4" t="s">
         <v>101</v>
@@ -11800,28 +11819,28 @@
         <v>288</v>
       </c>
       <c r="E249" s="4" t="s">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="F249" s="4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="G249" s="4">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="H249" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I249" s="4" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="J249" s="4" t="s">
-        <v>13</v>
+        <v>182</v>
       </c>
       <c r="K249" s="4">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="L249" s="4" t="s">
-        <v>39</v>
+        <v>183</v>
       </c>
     </row>
     <row r="250" spans="1:12">
@@ -11838,28 +11857,28 @@
         <v>288</v>
       </c>
       <c r="E250" s="4" t="s">
-        <v>368</v>
+        <v>238</v>
       </c>
       <c r="F250" s="4" t="s">
-        <v>290</v>
+        <v>307</v>
       </c>
       <c r="G250" s="4">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H250" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I250" s="4" t="s">
-        <v>90</v>
+        <v>371</v>
       </c>
       <c r="J250" s="4" t="s">
-        <v>13</v>
+        <v>76</v>
       </c>
       <c r="K250" s="4">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="L250" s="4" t="s">
-        <v>39</v>
+        <v>239</v>
       </c>
     </row>
     <row r="251" spans="1:12">
@@ -11876,28 +11895,28 @@
         <v>288</v>
       </c>
       <c r="E251" s="4" t="s">
-        <v>369</v>
+        <v>240</v>
       </c>
       <c r="F251" s="4" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="G251" s="4">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H251" s="4" t="s">
         <v>291</v>
       </c>
       <c r="I251" s="4" t="s">
-        <v>147</v>
+        <v>371</v>
       </c>
       <c r="J251" s="4" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="K251" s="4">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="L251" s="4" t="s">
-        <v>292</v>
+        <v>239</v>
       </c>
     </row>
     <row r="252" spans="1:12">
@@ -11910,39 +11929,153 @@
       <c r="C252" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="D252" s="4" t="s">
+      <c r="D252" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="E252" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="F252" s="4" t="s">
+      <c r="E252" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F252" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="G252" s="7">
+        <v>1</v>
+      </c>
+      <c r="H252" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="I252" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="J252" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K252" s="7">
+        <v>2024</v>
+      </c>
+      <c r="L252" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="253" spans="1:12">
+      <c r="A253" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B253" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C253" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D253" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="E253" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="F253" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="G253" s="8">
+        <v>1</v>
+      </c>
+      <c r="H253" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="I253" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="J253" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K253" s="8">
+        <v>2024</v>
+      </c>
+      <c r="L253" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="254" spans="1:12">
+      <c r="A254" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B254" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C254" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D254" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="E254" s="8" t="s">
+        <v>373</v>
+      </c>
+      <c r="F254" s="8" t="s">
+        <v>299</v>
+      </c>
+      <c r="G254" s="8">
+        <v>1</v>
+      </c>
+      <c r="H254" s="8" t="s">
+        <v>291</v>
+      </c>
+      <c r="I254" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="J254" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="K254" s="8">
+        <v>2024</v>
+      </c>
+      <c r="L254" s="8" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="255" spans="1:12">
+      <c r="A255" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B255" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C255" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="D255" s="8" t="s">
+        <v>288</v>
+      </c>
+      <c r="E255" s="8" t="s">
+        <v>374</v>
+      </c>
+      <c r="F255" s="8" t="s">
         <v>303</v>
       </c>
-      <c r="G252" s="4">
+      <c r="G255" s="8">
         <v>1</v>
       </c>
-      <c r="H252" s="4" t="s">
+      <c r="H255" s="8" t="s">
         <v>291</v>
       </c>
-      <c r="I252" s="4" t="s">
+      <c r="I255" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="J252" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="K252" s="6">
+      <c r="J255" s="8" t="s">
+        <v>357</v>
+      </c>
+      <c r="K255" s="8">
         <v>2024</v>
       </c>
-      <c r="L252" s="6" t="s">
-        <v>354</v>
+      <c r="L255" s="8" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:L252">
-    <sortCondition ref="H2:H252"/>
-    <sortCondition ref="C2:C252"/>
-    <sortCondition ref="E2:E252"/>
+  <sortState ref="A2:L255">
+    <sortCondition ref="H2:H255"/>
+    <sortCondition ref="C2:C255"/>
+    <sortCondition ref="E2:E255"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
